--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -662,12 +662,16 @@
           <t>NSE:ADANIPORTS26SEP1640PE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-01 11:53:27</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,11 +667,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-09-01 11:53:27</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,101 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:05:48</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>267</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>267</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1725</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="U3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:ITC26SEP267.5PE</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -756,12 +756,16 @@
           <t>NSE:ITC26SEP267.5PE</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:12:03</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,11 +761,101 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-09-01 12:12:03</t>
-        </is>
-      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:15:09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1010.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1010</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="K4" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="L4" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="M4" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="N4" t="n">
+        <v>525</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="U4" t="n">
+        <v>28</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:MAXHEALTH26SEP1010PE</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -850,12 +850,16 @@
           <t>NSE:MAXHEALTH26SEP1010PE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:18:14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -761,6 +761,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:19:46</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -860,11 +860,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-09-01 12:18:14</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -860,7 +860,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:30:32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,6 +865,101 @@
           <t>2026-09-01 12:30:32</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:38:12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>204.99</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H5" t="n">
+        <v>205</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3550</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="S5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="U5" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:ADANIPOWER26SEP205PE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,6 +667,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:05:56</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -954,12 +959,6 @@
           <t>NSE:ADANIPOWER26SEP205PE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,11 +667,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-09-01 13:05:56</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -955,6 +954,101 @@
           <t>NSE:ADANIPOWER26SEP205PE</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:18:13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>267.15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H6" t="n">
+        <v>267</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1725</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="U6" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:ITC26SEP267.5PE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -954,6 +954,16 @@
           <t>NSE:ADANIPOWER26SEP205PE</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:42:51</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1043,12 +1053,6 @@
           <t>NSE:ITC26SEP267.5PE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -959,11 +959,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-09-01 13:42:51</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -959,7 +959,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:52:07</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,6 +667,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:02:52</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -1058,6 +1058,16 @@
           <t>NSE:ITC26SEP267.5PE</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:07:27</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -1063,11 +1063,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:07:27</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,11 +667,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:02:52</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1063,7 +1059,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,7 +667,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:13:38</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -1063,6 +1063,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:15:09</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -1063,11 +1063,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:15:09</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -1063,7 +1063,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:24:12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -1063,11 +1063,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:24:12</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,11 +667,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:13:38</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1063,7 +1059,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,7 +667,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:33:32</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,11 +667,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:33:32</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,7 +667,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:36:36</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,11 +667,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:36:36</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,7 +667,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:44:30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,11 +667,7 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-09-01 14:44:30</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1059,6 +1058,101 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:02:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="H7" t="n">
+        <v>290</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="M7" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1900</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>61.48</v>
+      </c>
+      <c r="U7" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:PETRONET26SEP290CE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -667,6 +667,11 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:03:36</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1147,12 +1152,16 @@
           <t>NSE:PETRONET26SEP290CE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:03:36</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,6 +1162,101 @@
           <t>2026-09-01 15:03:36</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:13:04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>337.75</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="H8" t="n">
+        <v>340</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="M8" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3125</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="S8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:NYKAA26SEP340CE</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -860,9 +860,14 @@
           <t>NSE:MAXHEALTH26SEP1010PE</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:15:27</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 1 Hit</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1251,12 +1256,6 @@
           <t>NSE:NYKAA26SEP340CE</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,11 +667,6 @@
           <t>Expired (no SL/Target hit)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-09-01 15:03:36</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1254,6 +1249,115 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:NYKAA26SEP340CE</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Expired (no SL/Target hit)</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:16:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:16:18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1003</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1010</v>
+      </c>
+      <c r="I9" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="K9" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="L9" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="M9" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="N9" t="n">
+        <v>525</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="U9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:MAXHEALTH26SEP1010PE</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:16:19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -1355,9 +1355,14 @@
           <t>2026-09-01 15:16:19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:20:59</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/signals_2026-09-01.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,6 +1365,190 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:30:14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1265</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.39</v>
+      </c>
+      <c r="K10" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="M10" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="N10" t="n">
+        <v>600</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S10" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:ADANIGREEN26SEP1260PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:30:14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>204.36</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>205</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3550</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="S11" t="n">
+        <v>29</v>
+      </c>
+      <c r="T11" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="U11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:ADANIPOWER26SEP205PE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
